--- a/evaluation/results/Qualitative-Evaluation-Case2.xlsx
+++ b/evaluation/results/Qualitative-Evaluation-Case2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Code\scripts\results\Qualitative Results with LAI2F\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21591DC5-D82E-4F9D-885D-5475F4A4E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10800" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="6" r:id="rId1"/>
@@ -18,13 +19,19 @@
     <sheet name="mat" sheetId="3" r:id="rId4"/>
     <sheet name="oek" sheetId="4" r:id="rId5"/>
     <sheet name="ver" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="26">
   <si>
     <t>Team</t>
   </si>
@@ -77,22 +84,37 @@
     <t>f1@20</t>
   </si>
   <si>
-    <t>LA²I²F</t>
+    <t>Rank</t>
   </si>
   <si>
-    <t>Annif</t>
+    <t>System 3</t>
   </si>
   <si>
-    <t>DNB-AI-Project</t>
+    <t>System 2</t>
   </si>
   <si>
-    <t>Rank</t>
+    <t>System 1</t>
+  </si>
+  <si>
+    <t>Linguistics</t>
+  </si>
+  <si>
+    <t>Literature Studies</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Economics</t>
+  </si>
+  <si>
+    <t>Traffic engineering</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -163,6 +185,1487 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ndcg@5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$3:$C$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$B$3:$C$5,Sheet1!$B$7:$C$9,Sheet1!$B$11:$C$13,Sheet1!$B$15:$C$17,Sheet1!$B$19:$C$21)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Linguistics</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Literature Studies</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mathematics</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Economics</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Traffic engineering</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$D$3:$D$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$D$3:$D$5,Sheet1!$D$7:$D$9,Sheet1!$D$11:$D$13,Sheet1!$D$15:$D$17,Sheet1!$D$19:$D$21)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.29260000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.56540000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.629</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45150000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.45119999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.55489999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.31559999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.71709999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69879999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54320000000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.68330000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.89990000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.39E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.66610000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.77890000000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7247-4F52-BC6D-B92680E5EB7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ndcg@10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$3:$C$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$B$3:$C$5,Sheet1!$B$7:$C$9,Sheet1!$B$11:$C$13,Sheet1!$B$15:$C$17,Sheet1!$B$19:$C$21)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Linguistics</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Literature Studies</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mathematics</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Economics</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Traffic engineering</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$E$3:$E$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$E$3:$E$5,Sheet1!$E$7:$E$9,Sheet1!$E$11:$E$13,Sheet1!$E$15:$E$17,Sheet1!$E$19:$E$21)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.3422</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.55530000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.62539999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.45810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.41510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.56269999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.33689999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.71709999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.66649999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.57320000000000004</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.78520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.4900000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.59089999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.67249999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7247-4F52-BC6D-B92680E5EB7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ndcg@15</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$3:$C$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$B$3:$C$5,Sheet1!$B$7:$C$9,Sheet1!$B$11:$C$13,Sheet1!$B$15:$C$17,Sheet1!$B$19:$C$21)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Linguistics</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Literature Studies</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mathematics</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Economics</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Traffic engineering</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$F$3:$F$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$F$3:$F$5,Sheet1!$F$7:$F$9,Sheet1!$F$11:$F$13,Sheet1!$F$15:$F$17,Sheet1!$F$19:$F$21)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.41520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.55530000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67789999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48609999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.41510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5746</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.4168</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.71709999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.78690000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.61429999999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.82689999999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1439</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.59089999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.72640000000000005</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7247-4F52-BC6D-B92680E5EB7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ndcg@20</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$3:$C$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$B$3:$C$5,Sheet1!$B$7:$C$9,Sheet1!$B$11:$C$13,Sheet1!$B$15:$C$17,Sheet1!$B$19:$C$21)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>System 1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>System 2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>System 3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Linguistics</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Literature Studies</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mathematics</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Economics</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Traffic engineering</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$G$3:$G$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$G$3:$G$5,Sheet1!$G$7:$G$9,Sheet1!$G$11:$G$13,Sheet1!$G$15:$G$17,Sheet1!$G$19:$G$21)</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0.42809999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.55530000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69779999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.51780000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.41510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6079</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.46970000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.71709999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.84130000000000005</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.64770000000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.89590000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.27379999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.59089999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.80649999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7247-4F52-BC6D-B92680E5EB7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="928913935"/>
+        <c:axId val="932916239"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="928913935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="932916239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="932916239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="928913935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83CDDD58-9CE1-B81C-2D68-5E4B9001E78E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,7 +1952,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -475,7 +1978,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -646,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
         <v>0.24</v>
@@ -703,7 +2206,260 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.54</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.52139999999999997</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.629</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.53049999999999997</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.63439999999999996</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.62539999999999996</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.43419999999999997</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.26669999999999999</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.74329999999999996</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.67789999999999995</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.3926</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.215</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0.69779999999999998</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.3377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.51290000000000002</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.56540000000000001</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.43659999999999999</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.51290000000000002</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.27729999999999999</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.12670000000000001</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.51290000000000002</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="N3" s="2">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0.51290000000000002</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.26790000000000003</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.21529999999999999</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.39879999999999999</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.3422</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.2072</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.64880000000000004</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0.41520000000000001</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.17330000000000001</v>
+      </c>
+      <c r="N4" s="2">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="O4" s="2">
+        <v>0.6774</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.42809999999999998</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D11" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -784,158 +2540,158 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="C2" s="2">
-        <v>0.52139999999999997</v>
+        <v>0.42330000000000001</v>
       </c>
       <c r="D2" s="2">
-        <v>0.629</v>
+        <v>0.55489999999999995</v>
       </c>
       <c r="E2" s="2">
-        <v>0.53049999999999997</v>
+        <v>0.45850000000000002</v>
       </c>
       <c r="F2" s="2">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G2" s="2">
-        <v>0.63439999999999996</v>
+        <v>0.58609999999999995</v>
       </c>
       <c r="H2" s="2">
-        <v>0.62539999999999996</v>
+        <v>0.56269999999999998</v>
       </c>
       <c r="I2" s="2">
-        <v>0.43419999999999997</v>
+        <v>0.43830000000000002</v>
       </c>
       <c r="J2" s="2">
-        <v>0.26669999999999999</v>
+        <v>0.2467</v>
       </c>
       <c r="K2" s="2">
-        <v>0.74329999999999996</v>
+        <v>0.60609999999999997</v>
       </c>
       <c r="L2" s="2">
-        <v>0.67789999999999995</v>
+        <v>0.5746</v>
       </c>
       <c r="M2" s="2">
-        <v>0.3926</v>
+        <v>0.35070000000000001</v>
       </c>
       <c r="N2" s="2">
-        <v>0.215</v>
+        <v>0.2</v>
       </c>
       <c r="O2" s="2">
-        <v>0.78700000000000003</v>
+        <v>0.68110000000000004</v>
       </c>
       <c r="P2" s="3">
-        <v>0.69779999999999998</v>
+        <v>0.6079</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.3377</v>
+        <v>0.30919999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="C3" s="2">
-        <v>0.51290000000000002</v>
+        <v>0.31640000000000001</v>
       </c>
       <c r="D3" s="2">
-        <v>0.56540000000000001</v>
+        <v>0.45150000000000001</v>
       </c>
       <c r="E3" s="2">
-        <v>0.43659999999999999</v>
+        <v>0.33679999999999999</v>
       </c>
       <c r="F3" s="2">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="G3" s="2">
-        <v>0.51290000000000002</v>
+        <v>0.44790000000000002</v>
       </c>
       <c r="H3" s="2">
-        <v>0.55530000000000002</v>
+        <v>0.45810000000000001</v>
       </c>
       <c r="I3" s="2">
-        <v>0.27729999999999999</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="J3" s="2">
-        <v>0.12670000000000001</v>
+        <v>0.21329999999999999</v>
       </c>
       <c r="K3" s="2">
-        <v>0.51290000000000002</v>
+        <v>0.54449999999999998</v>
       </c>
       <c r="L3" s="2">
-        <v>0.55530000000000002</v>
+        <v>0.48609999999999998</v>
       </c>
       <c r="M3" s="2">
-        <v>0.20319999999999999</v>
+        <v>0.30649999999999999</v>
       </c>
       <c r="N3" s="2">
-        <v>9.5000000000000001E-2</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="O3" s="2">
-        <v>0.51290000000000002</v>
+        <v>0.6018</v>
       </c>
       <c r="P3" s="3">
-        <v>0.55530000000000002</v>
+        <v>0.51780000000000004</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.1603</v>
+        <v>0.29459999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="C4" s="2">
-        <v>0.26790000000000003</v>
+        <v>0.33510000000000001</v>
       </c>
       <c r="D4" s="2">
-        <v>0.29260000000000003</v>
+        <v>0.45119999999999999</v>
       </c>
       <c r="E4" s="2">
-        <v>0.21529999999999999</v>
+        <v>0.32740000000000002</v>
       </c>
       <c r="F4" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="G4" s="2">
-        <v>0.39879999999999999</v>
+        <v>0.33510000000000001</v>
       </c>
       <c r="H4" s="2">
-        <v>0.3422</v>
+        <v>0.41510000000000002</v>
       </c>
       <c r="I4" s="2">
-        <v>0.2072</v>
+        <v>0.21659999999999999</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1</v>
+        <v>0.1067</v>
       </c>
       <c r="K4" s="2">
-        <v>0.64880000000000004</v>
+        <v>0.33510000000000001</v>
       </c>
       <c r="L4" s="2">
-        <v>0.41520000000000001</v>
+        <v>0.41510000000000002</v>
       </c>
       <c r="M4" s="2">
-        <v>0.17330000000000001</v>
+        <v>0.16189999999999999</v>
       </c>
       <c r="N4" s="2">
-        <v>8.5000000000000006E-2</v>
+        <v>0.08</v>
       </c>
       <c r="O4" s="2">
-        <v>0.6774</v>
+        <v>0.33510000000000001</v>
       </c>
       <c r="P4" s="3">
-        <v>0.42809999999999998</v>
+        <v>0.41510000000000002</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.151</v>
+        <v>0.12920000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -943,8 +2699,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1025,158 +2781,158 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
+        <v>0.62</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.39050000000000001</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.69879999999999998</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.47920000000000001</v>
+      </c>
+      <c r="F2" s="2">
         <v>0.5</v>
       </c>
-      <c r="C2" s="2">
-        <v>0.42330000000000001</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.55489999999999995</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.45850000000000002</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.35</v>
-      </c>
       <c r="G2" s="2">
-        <v>0.58609999999999995</v>
+        <v>0.60860000000000003</v>
       </c>
       <c r="H2" s="2">
-        <v>0.56269999999999998</v>
+        <v>0.66649999999999998</v>
       </c>
       <c r="I2" s="2">
-        <v>0.43830000000000002</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="J2" s="2">
-        <v>0.2467</v>
+        <v>0.46</v>
       </c>
       <c r="K2" s="2">
-        <v>0.60609999999999997</v>
+        <v>0.83809999999999996</v>
       </c>
       <c r="L2" s="2">
-        <v>0.5746</v>
+        <v>0.78690000000000004</v>
       </c>
       <c r="M2" s="2">
-        <v>0.35070000000000001</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="N2" s="2">
-        <v>0.2</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="O2" s="2">
-        <v>0.68110000000000004</v>
+        <v>0.9456</v>
       </c>
       <c r="P2" s="3">
-        <v>0.6079</v>
+        <v>0.84130000000000005</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.30919999999999997</v>
+        <v>0.55720000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="C3" s="2">
-        <v>0.31640000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="D3" s="2">
-        <v>0.45150000000000001</v>
+        <v>0.71709999999999996</v>
       </c>
       <c r="E3" s="2">
-        <v>0.33679999999999999</v>
+        <v>0.50509999999999999</v>
       </c>
       <c r="F3" s="2">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G3" s="2">
-        <v>0.44790000000000002</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H3" s="2">
-        <v>0.45810000000000001</v>
+        <v>0.71709999999999996</v>
       </c>
       <c r="I3" s="2">
-        <v>0.32900000000000001</v>
+        <v>0.30959999999999999</v>
       </c>
       <c r="J3" s="2">
-        <v>0.21329999999999999</v>
+        <v>0.1333</v>
       </c>
       <c r="K3" s="2">
-        <v>0.54449999999999998</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="L3" s="2">
-        <v>0.48609999999999998</v>
+        <v>0.71709999999999996</v>
       </c>
       <c r="M3" s="2">
-        <v>0.30649999999999999</v>
+        <v>0.22320000000000001</v>
       </c>
       <c r="N3" s="2">
-        <v>0.19500000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O3" s="2">
-        <v>0.6018</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="P3" s="3">
-        <v>0.51780000000000004</v>
+        <v>0.71709999999999996</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.29459999999999997</v>
+        <v>0.17449999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="C4" s="2">
-        <v>0.33510000000000001</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="D4" s="2">
-        <v>0.45119999999999999</v>
+        <v>0.31559999999999999</v>
       </c>
       <c r="E4" s="2">
-        <v>0.32740000000000002</v>
+        <v>0.27489999999999998</v>
       </c>
       <c r="F4" s="2">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="G4" s="2">
-        <v>0.33510000000000001</v>
+        <v>0.4194</v>
       </c>
       <c r="H4" s="2">
-        <v>0.41510000000000002</v>
+        <v>0.33689999999999998</v>
       </c>
       <c r="I4" s="2">
-        <v>0.21659999999999999</v>
+        <v>0.27989999999999998</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1067</v>
+        <v>0.1933</v>
       </c>
       <c r="K4" s="2">
-        <v>0.33510000000000001</v>
+        <v>0.60729999999999995</v>
       </c>
       <c r="L4" s="2">
-        <v>0.41510000000000002</v>
+        <v>0.4168</v>
       </c>
       <c r="M4" s="2">
-        <v>0.16189999999999999</v>
+        <v>0.29330000000000001</v>
       </c>
       <c r="N4" s="2">
-        <v>0.08</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="O4" s="2">
-        <v>0.33510000000000001</v>
+        <v>0.74380000000000002</v>
       </c>
       <c r="P4" s="3">
-        <v>0.41510000000000002</v>
+        <v>0.46970000000000001</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.12920000000000001</v>
+        <v>0.2833</v>
       </c>
     </row>
   </sheetData>
@@ -1184,8 +2940,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1266,158 +3022,158 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="C2" s="2">
-        <v>0.39050000000000001</v>
+        <v>0.47720000000000001</v>
       </c>
       <c r="D2" s="2">
-        <v>0.69879999999999998</v>
+        <v>0.89990000000000003</v>
       </c>
       <c r="E2" s="2">
-        <v>0.47920000000000001</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="F2" s="2">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="G2" s="2">
-        <v>0.60860000000000003</v>
+        <v>0.66390000000000005</v>
       </c>
       <c r="H2" s="2">
-        <v>0.66649999999999998</v>
+        <v>0.78520000000000001</v>
       </c>
       <c r="I2" s="2">
-        <v>0.54900000000000004</v>
+        <v>0.60160000000000002</v>
       </c>
       <c r="J2" s="2">
-        <v>0.46</v>
+        <v>0.44669999999999999</v>
       </c>
       <c r="K2" s="2">
-        <v>0.83809999999999996</v>
+        <v>0.79159999999999997</v>
       </c>
       <c r="L2" s="2">
-        <v>0.78690000000000004</v>
+        <v>0.82689999999999997</v>
       </c>
       <c r="M2" s="2">
-        <v>0.59399999999999997</v>
+        <v>0.57110000000000005</v>
       </c>
       <c r="N2" s="2">
-        <v>0.39500000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="O2" s="2">
-        <v>0.9456</v>
+        <v>0.92520000000000002</v>
       </c>
       <c r="P2" s="3">
-        <v>0.84130000000000005</v>
+        <v>0.89590000000000003</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.55720000000000003</v>
+        <v>0.5585</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>0.4</v>
       </c>
       <c r="C3" s="2">
-        <v>0.68500000000000005</v>
+        <v>0.47289999999999999</v>
       </c>
       <c r="D3" s="2">
-        <v>0.71709999999999996</v>
+        <v>0.54320000000000002</v>
       </c>
       <c r="E3" s="2">
-        <v>0.50509999999999999</v>
+        <v>0.43340000000000001</v>
       </c>
       <c r="F3" s="2">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G3" s="2">
-        <v>0.68500000000000005</v>
+        <v>0.60680000000000001</v>
       </c>
       <c r="H3" s="2">
-        <v>0.71709999999999996</v>
+        <v>0.57320000000000004</v>
       </c>
       <c r="I3" s="2">
-        <v>0.30959999999999999</v>
+        <v>0.38319999999999999</v>
       </c>
       <c r="J3" s="2">
-        <v>0.1333</v>
+        <v>0.22</v>
       </c>
       <c r="K3" s="2">
-        <v>0.68500000000000005</v>
+        <v>0.69730000000000003</v>
       </c>
       <c r="L3" s="2">
-        <v>0.71709999999999996</v>
+        <v>0.61429999999999996</v>
       </c>
       <c r="M3" s="2">
-        <v>0.22320000000000001</v>
+        <v>0.33450000000000002</v>
       </c>
       <c r="N3" s="2">
-        <v>0.1</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="O3" s="2">
-        <v>0.68500000000000005</v>
+        <v>0.76290000000000002</v>
       </c>
       <c r="P3" s="3">
-        <v>0.71709999999999996</v>
+        <v>0.64770000000000005</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.17449999999999999</v>
+        <v>0.31059999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="C4" s="2">
-        <v>0.29160000000000003</v>
+        <v>0.54290000000000005</v>
       </c>
       <c r="D4" s="2">
-        <v>0.31559999999999999</v>
+        <v>0.68330000000000002</v>
       </c>
       <c r="E4" s="2">
-        <v>0.27489999999999998</v>
+        <v>0.47360000000000002</v>
       </c>
       <c r="F4" s="2">
         <v>0.21</v>
       </c>
       <c r="G4" s="2">
-        <v>0.4194</v>
+        <v>0.54290000000000005</v>
       </c>
       <c r="H4" s="2">
-        <v>0.33689999999999998</v>
+        <v>0.64</v>
       </c>
       <c r="I4" s="2">
-        <v>0.27989999999999998</v>
+        <v>0.3029</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1933</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K4" s="2">
-        <v>0.60729999999999995</v>
+        <v>0.54290000000000005</v>
       </c>
       <c r="L4" s="2">
-        <v>0.4168</v>
+        <v>0.64</v>
       </c>
       <c r="M4" s="2">
-        <v>0.29330000000000001</v>
+        <v>0.22259999999999999</v>
       </c>
       <c r="N4" s="2">
-        <v>0.17499999999999999</v>
+        <v>0.105</v>
       </c>
       <c r="O4" s="2">
-        <v>0.74380000000000002</v>
+        <v>0.54290000000000005</v>
       </c>
       <c r="P4" s="3">
-        <v>0.46970000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.2833</v>
+        <v>0.17599999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1425,8 +3181,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1507,158 +3263,158 @@
         <v>18</v>
       </c>
       <c r="B2" s="2">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="C2" s="2">
-        <v>0.47720000000000001</v>
+        <v>0.32840000000000003</v>
       </c>
       <c r="D2" s="2">
-        <v>0.89990000000000003</v>
+        <v>0.77890000000000004</v>
       </c>
       <c r="E2" s="2">
-        <v>0.57399999999999995</v>
+        <v>0.43409999999999999</v>
       </c>
       <c r="F2" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.54</v>
       </c>
       <c r="G2" s="2">
-        <v>0.66390000000000005</v>
+        <v>0.53110000000000002</v>
       </c>
       <c r="H2" s="2">
-        <v>0.78520000000000001</v>
+        <v>0.67249999999999999</v>
       </c>
       <c r="I2" s="2">
-        <v>0.60160000000000002</v>
+        <v>0.53549999999999998</v>
       </c>
       <c r="J2" s="2">
-        <v>0.44669999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="K2" s="2">
-        <v>0.79159999999999997</v>
+        <v>0.68259999999999998</v>
       </c>
       <c r="L2" s="2">
-        <v>0.82689999999999997</v>
+        <v>0.72640000000000005</v>
       </c>
       <c r="M2" s="2">
-        <v>0.57110000000000005</v>
+        <v>0.54959999999999998</v>
       </c>
       <c r="N2" s="2">
-        <v>0.4</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="O2" s="2">
-        <v>0.92520000000000002</v>
+        <v>0.83160000000000001</v>
       </c>
       <c r="P2" s="3">
-        <v>0.89590000000000003</v>
+        <v>0.80649999999999999</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.5585</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="C3" s="2">
-        <v>0.47289999999999999</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="D3" s="2">
-        <v>0.54320000000000002</v>
+        <v>0.66610000000000003</v>
       </c>
       <c r="E3" s="2">
-        <v>0.43340000000000001</v>
+        <v>0.48209999999999997</v>
       </c>
       <c r="F3" s="2">
-        <v>0.28000000000000003</v>
+        <v>0.22</v>
       </c>
       <c r="G3" s="2">
-        <v>0.60680000000000001</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="H3" s="2">
-        <v>0.57320000000000004</v>
+        <v>0.59089999999999998</v>
       </c>
       <c r="I3" s="2">
-        <v>0.38319999999999999</v>
+        <v>0.31140000000000001</v>
       </c>
       <c r="J3" s="2">
-        <v>0.22</v>
+        <v>0.1467</v>
       </c>
       <c r="K3" s="2">
-        <v>0.69730000000000003</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="L3" s="2">
-        <v>0.61429999999999996</v>
+        <v>0.59089999999999998</v>
       </c>
       <c r="M3" s="2">
-        <v>0.33450000000000002</v>
+        <v>0.2301</v>
       </c>
       <c r="N3" s="2">
-        <v>0.19500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="O3" s="2">
-        <v>0.76290000000000002</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="P3" s="3">
-        <v>0.64770000000000005</v>
+        <v>0.59089999999999998</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.31059999999999999</v>
+        <v>0.18240000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
-        <v>0.54290000000000005</v>
+        <v>0.01</v>
       </c>
       <c r="D4" s="2">
-        <v>0.68330000000000002</v>
+        <v>3.39E-2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.47360000000000002</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="G4" s="2">
-        <v>0.54290000000000005</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="H4" s="2">
-        <v>0.64</v>
+        <v>4.4900000000000002E-2</v>
       </c>
       <c r="I4" s="2">
-        <v>0.3029</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="J4" s="2">
-        <v>0.14000000000000001</v>
+        <v>0.1133</v>
       </c>
       <c r="K4" s="2">
-        <v>0.54290000000000005</v>
+        <v>0.2492</v>
       </c>
       <c r="L4" s="2">
-        <v>0.64</v>
+        <v>0.1439</v>
       </c>
       <c r="M4" s="2">
-        <v>0.22259999999999999</v>
+        <v>0.15579999999999999</v>
       </c>
       <c r="N4" s="2">
-        <v>0.105</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="O4" s="2">
-        <v>0.54290000000000005</v>
+        <v>0.57030000000000003</v>
       </c>
       <c r="P4" s="3">
-        <v>0.64</v>
+        <v>0.27379999999999999</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.17599999999999999</v>
+        <v>0.26779999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1666,243 +3422,361 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23C2FED-C671-449A-AE67-8CF845F34A1C}">
+  <dimension ref="B2:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.3422</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.41520000000000001</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.42809999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.56540000000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.55530000000000002</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.55530000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="2">
+      <c r="D5" s="2">
+        <v>0.629</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.62539999999999996</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.67789999999999995</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.69779999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.45150000000000001</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.45810000000000001</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.48609999999999998</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.51780000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.45119999999999999</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.41510000000000002</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.41510000000000002</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.41510000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.55489999999999995</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.56269999999999998</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.5746</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.6079</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.31559999999999999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.33689999999999998</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.4168</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.46970000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.71709999999999996</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.71709999999999996</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.71709999999999996</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.71709999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.69879999999999998</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.66649999999999998</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.78690000000000004</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.84130000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.54320000000000002</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.57320000000000004</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.61429999999999996</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.64770000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.68330000000000002</v>
+      </c>
+      <c r="E16" s="2">
         <v>0.64</v>
       </c>
-      <c r="C2" s="2">
-        <v>0.32840000000000003</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="F16" s="2">
+        <v>0.64</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.89990000000000003</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.78520000000000001</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.82689999999999997</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.89590000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3.39E-2</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.1439</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.27379999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.66610000000000003</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.59089999999999998</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.59089999999999998</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.59089999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2">
         <v>0.77890000000000004</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.43409999999999999</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.54</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.53110000000000002</v>
-      </c>
-      <c r="H2" s="2">
+      <c r="E21" s="2">
         <v>0.67249999999999999</v>
       </c>
-      <c r="I2" s="2">
-        <v>0.53549999999999998</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.46</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.68259999999999998</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="F21" s="2">
         <v>0.72640000000000005</v>
       </c>
-      <c r="M2" s="2">
-        <v>0.54959999999999998</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.83160000000000001</v>
-      </c>
-      <c r="P2" s="3">
+      <c r="G21" s="3">
         <v>0.80649999999999999</v>
       </c>
-      <c r="Q2" s="2">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.44</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.66610000000000003</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.48209999999999997</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.22</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.59089999999999998</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.31140000000000001</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.1467</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0.59089999999999998</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0.2301</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0.11</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.59089999999999998</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>0.18240000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3.39E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="G4" s="2">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>4.4900000000000002E-2</v>
-      </c>
-      <c r="I4" s="2">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.1133</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.2492</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.1439</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0.15579999999999999</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0.57030000000000003</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.27379999999999999</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0.26779999999999998</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/evaluation/results/Qualitative-Evaluation-Case2.xlsx
+++ b/evaluation/results/Qualitative-Evaluation-Case2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21591DC5-D82E-4F9D-885D-5475F4A4E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BEF5F8-E0B1-4ADA-ABC2-BA8C918643D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="6" r:id="rId1"/>
@@ -956,6 +956,7 @@
         <c:axId val="932916239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1.2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>

--- a/evaluation/results/Qualitative-Evaluation-Case2.xlsx
+++ b/evaluation/results/Qualitative-Evaluation-Case2.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSouzaJ\Datasets\subject-indexing-dataset\evaluation\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SadruddinS\Data\GermEval25\Code\subject-indexing-dataset\evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BEF5F8-E0B1-4ADA-ABC2-BA8C918643D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Overall" sheetId="6" r:id="rId1"/>
@@ -114,7 +113,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -343,7 +342,7 @@
                   <c:v>0.55489999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.31559999999999999</c:v>
+                  <c:v>0.32950000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.71709999999999996</c:v>
@@ -361,7 +360,7 @@
                   <c:v>0.89990000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.39E-2</c:v>
+                  <c:v>0.32340000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.66610000000000003</c:v>
@@ -513,7 +512,7 @@
                   <c:v>0.56269999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.33689999999999998</c:v>
+                  <c:v>0.3518</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.71709999999999996</c:v>
@@ -531,7 +530,7 @@
                   <c:v>0.78520000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.4900000000000002E-2</c:v>
+                  <c:v>0.37109999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.59089999999999998</c:v>
@@ -683,7 +682,7 @@
                   <c:v>0.5746</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4168</c:v>
+                  <c:v>0.43120000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.71709999999999996</c:v>
@@ -701,7 +700,7 @@
                   <c:v>0.82689999999999997</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1439</c:v>
+                  <c:v>0.43009999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.59089999999999998</c:v>
@@ -853,7 +852,7 @@
                   <c:v>0.6079</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46970000000000001</c:v>
+                  <c:v>0.48509999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.71709999999999996</c:v>
@@ -871,7 +870,7 @@
                   <c:v>0.89590000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.27379999999999999</c:v>
+                  <c:v>0.45500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.59089999999999998</c:v>
@@ -942,7 +941,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="932916239"/>
@@ -1002,7 +1001,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="de-DE"/>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="928913935"/>
@@ -1019,6 +1018,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout/>
       <c:overlay val="1"/>
       <c:spPr>
         <a:noFill/>
@@ -1044,7 +1044,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1074,7 +1074,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="de-DE"/>
+      <a:endParaRPr lang="en-US"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1632,14 +1632,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:to>
@@ -1953,7 +1953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2153,52 +2153,52 @@
         <v>20</v>
       </c>
       <c r="C4" s="2">
-        <v>0.24</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="D4" s="2">
-        <v>0.27179999999999999</v>
+        <v>0.32240000000000002</v>
       </c>
       <c r="E4" s="2">
-        <v>0.32740000000000002</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="F4" s="2">
-        <v>0.25490000000000002</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>0.184</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="H4" s="2">
-        <v>0.3841</v>
+        <v>0.45950000000000002</v>
       </c>
       <c r="I4" s="2">
-        <v>0.35110000000000002</v>
+        <v>0.41930000000000001</v>
       </c>
       <c r="J4" s="2">
-        <v>0.24879999999999999</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="K4" s="2">
-        <v>0.16800000000000001</v>
+        <v>0.1867</v>
       </c>
       <c r="L4" s="2">
-        <v>0.5494</v>
+        <v>0.60970000000000002</v>
       </c>
       <c r="M4" s="2">
-        <v>0.4153</v>
+        <v>0.47539999999999999</v>
       </c>
       <c r="N4" s="2">
-        <v>0.25729999999999997</v>
+        <v>0.28589999999999999</v>
       </c>
       <c r="O4" s="2">
         <v>0.16500000000000001</v>
       </c>
       <c r="P4" s="2">
-        <v>0.67120000000000002</v>
+        <v>0.67959999999999998</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.46739999999999998</v>
+        <v>0.50670000000000004</v>
       </c>
       <c r="R4" s="2">
-        <v>0.26490000000000002</v>
+        <v>0.26550000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2207,7 +2207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2460,7 +2460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2701,7 +2701,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2891,49 +2891,49 @@
         <v>0.26</v>
       </c>
       <c r="C4" s="2">
-        <v>0.29160000000000003</v>
+        <v>0.31740000000000002</v>
       </c>
       <c r="D4" s="2">
-        <v>0.31559999999999999</v>
+        <v>0.32950000000000002</v>
       </c>
       <c r="E4" s="2">
-        <v>0.27489999999999998</v>
+        <v>0.2858</v>
       </c>
       <c r="F4" s="2">
         <v>0.21</v>
       </c>
       <c r="G4" s="2">
-        <v>0.4194</v>
+        <v>0.45710000000000001</v>
       </c>
       <c r="H4" s="2">
-        <v>0.33689999999999998</v>
+        <v>0.3518</v>
       </c>
       <c r="I4" s="2">
-        <v>0.27989999999999998</v>
+        <v>0.2878</v>
       </c>
       <c r="J4" s="2">
         <v>0.1933</v>
       </c>
       <c r="K4" s="2">
-        <v>0.60729999999999995</v>
+        <v>0.64370000000000005</v>
       </c>
       <c r="L4" s="2">
-        <v>0.4168</v>
+        <v>0.43120000000000003</v>
       </c>
       <c r="M4" s="2">
-        <v>0.29330000000000001</v>
+        <v>0.29730000000000001</v>
       </c>
       <c r="N4" s="2">
         <v>0.17499999999999999</v>
       </c>
       <c r="O4" s="2">
-        <v>0.74380000000000002</v>
+        <v>0.78569999999999995</v>
       </c>
       <c r="P4" s="3">
-        <v>0.46970000000000001</v>
+        <v>0.48509999999999998</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.2833</v>
+        <v>0.28620000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2942,7 +2942,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3183,7 +3183,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3370,40 +3370,40 @@
         <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="C4" s="2">
-        <v>0.01</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="D4" s="2">
-        <v>3.39E-2</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="F4" s="2">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="G4" s="2">
-        <v>4.7500000000000001E-2</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H4" s="2">
-        <v>4.4900000000000002E-2</v>
+        <v>0.37109999999999999</v>
       </c>
       <c r="I4" s="2">
-        <v>3.6799999999999999E-2</v>
+        <v>0.29620000000000002</v>
       </c>
       <c r="J4" s="2">
-        <v>0.1133</v>
+        <v>0.20669999999999999</v>
       </c>
       <c r="K4" s="2">
-        <v>0.2492</v>
+        <v>0.51419999999999999</v>
       </c>
       <c r="L4" s="2">
-        <v>0.1439</v>
+        <v>0.43009999999999998</v>
       </c>
       <c r="M4" s="2">
-        <v>0.15579999999999999</v>
+        <v>0.2949</v>
       </c>
       <c r="N4" s="2">
         <v>0.17499999999999999</v>
@@ -3412,7 +3412,7 @@
         <v>0.57030000000000003</v>
       </c>
       <c r="P4" s="3">
-        <v>0.27379999999999999</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="Q4" s="2">
         <v>0.26779999999999998</v>
@@ -3424,7 +3424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23C2FED-C671-449A-AE67-8CF845F34A1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3592,16 +3592,16 @@
         <v>20</v>
       </c>
       <c r="D11" s="2">
-        <v>0.31559999999999999</v>
+        <v>0.32950000000000002</v>
       </c>
       <c r="E11" s="2">
-        <v>0.33689999999999998</v>
+        <v>0.3518</v>
       </c>
       <c r="F11" s="2">
-        <v>0.4168</v>
+        <v>0.43120000000000003</v>
       </c>
       <c r="G11" s="3">
-        <v>0.46970000000000001</v>
+        <v>0.48509999999999998</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -3730,16 +3730,16 @@
         <v>20</v>
       </c>
       <c r="D19" s="2">
-        <v>3.39E-2</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="E19" s="2">
-        <v>4.4900000000000002E-2</v>
+        <v>0.37109999999999999</v>
       </c>
       <c r="F19" s="2">
-        <v>0.1439</v>
+        <v>0.43009999999999998</v>
       </c>
       <c r="G19" s="3">
-        <v>0.27379999999999999</v>
+        <v>0.45500000000000002</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
